--- a/Rel Website/backend/templates/REL LTC Template.xlsx
+++ b/Rel Website/backend/templates/REL LTC Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amkor-my.sharepoint.com/personal/francisnino_villanueva_amkor_com/Documents/Documents/GitHub/Rel Request Process Flow/Rel Website/backend/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{55472A56-189D-460A-834D-19C0FE061C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95678843-1ADF-4912-8683-FD0932B9F038}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="8_{55472A56-189D-460A-834D-19C0FE061C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B78F68D-4A9A-4534-B89D-92D23FB2DDF7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="55">
   <si>
     <t>Reliability Test Request Sheet</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -198,25 +198,16 @@
     <t>rev.0</t>
   </si>
   <si>
-    <t>Revision History:</t>
-  </si>
-  <si>
-    <t>rev#</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Reason</t>
-  </si>
-  <si>
-    <t>Initial</t>
-  </si>
-  <si>
     <t>RRS# 220260256</t>
   </si>
   <si>
     <t>Page 2 of 2</t>
+  </si>
+  <si>
+    <t>E : Engineering Evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spec No. 001-2150 </t>
   </si>
 </sst>
 </file>
@@ -883,7 +874,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -981,9 +972,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1131,6 +1119,63 @@
     <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1152,52 +1197,10 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1499,10 +1502,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -1800,7 +1799,9 @@
     <col min="5" max="5" width="6.42578125" style="1" customWidth="1"/>
     <col min="6" max="6" width="6.5703125" style="1" customWidth="1"/>
     <col min="7" max="7" width="7.140625" style="1" customWidth="1"/>
-    <col min="8" max="18" width="6.42578125" style="1" customWidth="1"/>
+    <col min="8" max="14" width="6.42578125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="8.140625" style="1" customWidth="1"/>
+    <col min="16" max="18" width="6.42578125" style="1" customWidth="1"/>
     <col min="19" max="19" width="10.5703125" style="1" customWidth="1"/>
     <col min="20" max="20" width="12.5703125" style="1" customWidth="1"/>
     <col min="21" max="21" width="0.42578125" style="1" customWidth="1"/>
@@ -1809,13 +1810,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:20" ht="18.75">
-      <c r="P2" s="104">
-        <f>D8</f>
-        <v>0</v>
-      </c>
-      <c r="Q2" s="105"/>
-      <c r="R2" s="105"/>
-      <c r="S2" s="105"/>
+      <c r="P2" s="82" t="str">
+        <f>F8</f>
+        <v>RRS# 220260256</v>
+      </c>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17"/>
+      <c r="S2" s="17"/>
     </row>
     <row r="3" spans="2:20" ht="32.25" customHeight="1">
       <c r="C3" s="2"/>
@@ -1824,9 +1825,9 @@
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
-      <c r="P3" s="82" t="str">
-        <f>F8</f>
-        <v>RRS# 220260256</v>
+      <c r="P3" s="81">
+        <f>D8</f>
+        <v>0</v>
       </c>
       <c r="Q3" s="17"/>
       <c r="R3" s="17"/>
@@ -1890,14 +1891,14 @@
         <v>2</v>
       </c>
       <c r="C8" s="6"/>
-      <c r="D8" s="62"/>
+      <c r="D8" s="61"/>
       <c r="E8" s="18"/>
-      <c r="F8" s="68" t="s">
-        <v>56</v>
-      </c>
-      <c r="G8" s="68"/>
-      <c r="H8" s="68"/>
-      <c r="I8" s="68"/>
+      <c r="F8" s="67" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" s="67"/>
+      <c r="H8" s="67"/>
+      <c r="I8" s="67"/>
       <c r="J8" s="7"/>
       <c r="K8" s="5" t="s">
         <v>3</v>
@@ -1905,10 +1906,10 @@
       <c r="L8" s="6"/>
       <c r="M8" s="6"/>
       <c r="N8" s="30"/>
-      <c r="O8" s="74"/>
-      <c r="P8" s="71"/>
-      <c r="Q8" s="71"/>
-      <c r="R8" s="71"/>
+      <c r="O8" s="73"/>
+      <c r="P8" s="70"/>
+      <c r="Q8" s="70"/>
+      <c r="R8" s="70"/>
       <c r="S8" s="6"/>
       <c r="T8" s="7"/>
     </row>
@@ -1917,7 +1918,7 @@
         <v>4</v>
       </c>
       <c r="C9" s="9"/>
-      <c r="D9" s="72"/>
+      <c r="D9" s="71"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
@@ -1930,7 +1931,7 @@
       <c r="L9" s="9"/>
       <c r="M9" s="9"/>
       <c r="N9" s="22"/>
-      <c r="O9" s="73"/>
+      <c r="O9" s="72"/>
       <c r="P9" s="9"/>
       <c r="Q9" s="9"/>
       <c r="R9" s="9"/>
@@ -1942,11 +1943,11 @@
         <v>6</v>
       </c>
       <c r="C10" s="9"/>
-      <c r="D10" s="72"/>
-      <c r="E10" s="69"/>
-      <c r="F10" s="69"/>
-      <c r="G10" s="69"/>
-      <c r="H10" s="69"/>
+      <c r="D10" s="71"/>
+      <c r="E10" s="68"/>
+      <c r="F10" s="68"/>
+      <c r="G10" s="68"/>
+      <c r="H10" s="68"/>
       <c r="I10" s="9"/>
       <c r="J10" s="11"/>
       <c r="K10" s="8" t="s">
@@ -1955,7 +1956,7 @@
       <c r="L10" s="9"/>
       <c r="M10" s="9"/>
       <c r="N10" s="22"/>
-      <c r="O10" s="73"/>
+      <c r="O10" s="72"/>
       <c r="P10" s="9"/>
       <c r="Q10" s="9"/>
       <c r="R10" s="9"/>
@@ -1967,11 +1968,11 @@
         <v>8</v>
       </c>
       <c r="C11" s="9"/>
-      <c r="D11" s="72"/>
-      <c r="E11" s="61"/>
-      <c r="F11" s="61"/>
-      <c r="G11" s="61"/>
-      <c r="H11" s="61"/>
+      <c r="D11" s="71"/>
+      <c r="E11" s="60"/>
+      <c r="F11" s="60"/>
+      <c r="G11" s="60"/>
+      <c r="H11" s="60"/>
       <c r="I11" s="9"/>
       <c r="J11" s="11"/>
       <c r="K11" s="8" t="s">
@@ -1980,7 +1981,7 @@
       <c r="L11" s="9"/>
       <c r="M11" s="9"/>
       <c r="N11" s="22"/>
-      <c r="O11" s="73"/>
+      <c r="O11" s="72"/>
       <c r="P11" s="9"/>
       <c r="Q11" s="9"/>
       <c r="R11" s="9"/>
@@ -1992,11 +1993,11 @@
         <v>10</v>
       </c>
       <c r="C12" s="9"/>
-      <c r="D12" s="72"/>
-      <c r="E12" s="61"/>
-      <c r="F12" s="61"/>
-      <c r="G12" s="61"/>
-      <c r="H12" s="61"/>
+      <c r="D12" s="71"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
       <c r="I12" s="9"/>
       <c r="J12" s="11"/>
       <c r="K12" s="8" t="s">
@@ -2005,7 +2006,7 @@
       <c r="L12" s="9"/>
       <c r="M12" s="9"/>
       <c r="N12" s="22"/>
-      <c r="O12" s="73"/>
+      <c r="O12" s="72"/>
       <c r="P12" s="9"/>
       <c r="Q12" s="9"/>
       <c r="R12" s="9"/>
@@ -2017,11 +2018,11 @@
         <v>12</v>
       </c>
       <c r="C13" s="9"/>
-      <c r="D13" s="72"/>
-      <c r="E13" s="61"/>
-      <c r="F13" s="61"/>
-      <c r="G13" s="61"/>
-      <c r="H13" s="61"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="60"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="60"/>
+      <c r="H13" s="60"/>
       <c r="I13" s="9"/>
       <c r="J13" s="11"/>
       <c r="K13" s="8" t="s">
@@ -2030,7 +2031,7 @@
       <c r="L13" s="9"/>
       <c r="M13" s="9"/>
       <c r="N13" s="22"/>
-      <c r="O13" s="73" t="s">
+      <c r="O13" s="72" t="s">
         <v>39</v>
       </c>
       <c r="P13" s="9"/>
@@ -2044,11 +2045,11 @@
         <v>14</v>
       </c>
       <c r="C14" s="9"/>
-      <c r="D14" s="72"/>
-      <c r="E14" s="70"/>
-      <c r="F14" s="70"/>
-      <c r="G14" s="70"/>
-      <c r="H14" s="70"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="69"/>
+      <c r="F14" s="69"/>
+      <c r="G14" s="69"/>
+      <c r="H14" s="69"/>
       <c r="I14" s="9"/>
       <c r="J14" s="11"/>
       <c r="K14" s="8" t="s">
@@ -2057,7 +2058,7 @@
       <c r="L14" s="9"/>
       <c r="M14" s="9"/>
       <c r="N14" s="22"/>
-      <c r="O14" s="73" t="s">
+      <c r="O14" s="72" t="s">
         <v>39</v>
       </c>
       <c r="P14" s="9"/>
@@ -2071,11 +2072,11 @@
         <v>16</v>
       </c>
       <c r="C15" s="9"/>
-      <c r="D15" s="72"/>
-      <c r="E15" s="61"/>
-      <c r="F15" s="61"/>
-      <c r="G15" s="61"/>
-      <c r="H15" s="61"/>
+      <c r="D15" s="71"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="60"/>
+      <c r="H15" s="60"/>
       <c r="I15" s="9"/>
       <c r="J15" s="11"/>
       <c r="K15" s="8" t="s">
@@ -2084,7 +2085,7 @@
       <c r="L15" s="9"/>
       <c r="M15" s="9"/>
       <c r="N15" s="22"/>
-      <c r="O15" s="73"/>
+      <c r="O15" s="72"/>
       <c r="P15" s="9"/>
       <c r="Q15" s="9"/>
       <c r="R15" s="9"/>
@@ -2096,11 +2097,11 @@
         <v>18</v>
       </c>
       <c r="C16" s="9"/>
-      <c r="D16" s="72"/>
-      <c r="E16" s="61"/>
-      <c r="F16" s="61"/>
-      <c r="G16" s="61"/>
-      <c r="H16" s="61"/>
+      <c r="D16" s="71"/>
+      <c r="E16" s="60"/>
+      <c r="F16" s="60"/>
+      <c r="G16" s="60"/>
+      <c r="H16" s="60"/>
       <c r="I16" s="9"/>
       <c r="J16" s="11"/>
       <c r="K16" s="8" t="s">
@@ -2109,7 +2110,7 @@
       <c r="L16" s="9"/>
       <c r="M16" s="9"/>
       <c r="N16" s="22"/>
-      <c r="O16" s="73"/>
+      <c r="O16" s="72"/>
       <c r="P16" s="9"/>
       <c r="Q16" s="9"/>
       <c r="R16" s="9"/>
@@ -2134,7 +2135,7 @@
       <c r="L17" s="9"/>
       <c r="M17" s="9"/>
       <c r="N17" s="22"/>
-      <c r="O17" s="73"/>
+      <c r="O17" s="72"/>
       <c r="P17" s="9"/>
       <c r="Q17" s="9"/>
       <c r="R17" s="9"/>
@@ -2142,27 +2143,27 @@
       <c r="T17" s="11"/>
     </row>
     <row r="18" spans="2:21" ht="40.15" customHeight="1" thickBot="1">
-      <c r="B18" s="56" t="s">
+      <c r="B18" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="57"/>
-      <c r="D18" s="58"/>
-      <c r="E18" s="57"/>
-      <c r="F18" s="57"/>
-      <c r="G18" s="57"/>
-      <c r="H18" s="57"/>
-      <c r="I18" s="57"/>
-      <c r="J18" s="57"/>
-      <c r="K18" s="57"/>
-      <c r="L18" s="57"/>
-      <c r="M18" s="57"/>
-      <c r="N18" s="57"/>
-      <c r="O18" s="57"/>
-      <c r="P18" s="57"/>
-      <c r="Q18" s="57"/>
-      <c r="R18" s="57"/>
-      <c r="S18" s="57"/>
-      <c r="T18" s="59"/>
+      <c r="C18" s="56"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="56"/>
+      <c r="F18" s="56"/>
+      <c r="G18" s="56"/>
+      <c r="H18" s="56"/>
+      <c r="I18" s="56"/>
+      <c r="J18" s="56"/>
+      <c r="K18" s="56"/>
+      <c r="L18" s="56"/>
+      <c r="M18" s="56"/>
+      <c r="N18" s="56"/>
+      <c r="O18" s="56"/>
+      <c r="P18" s="56"/>
+      <c r="Q18" s="56"/>
+      <c r="R18" s="56"/>
+      <c r="S18" s="56"/>
+      <c r="T18" s="58"/>
     </row>
     <row r="19" spans="2:21" ht="15" thickBot="1">
       <c r="B19" s="13"/>
@@ -2194,46 +2195,46 @@
       <c r="T20" s="16"/>
     </row>
     <row r="21" spans="2:21" ht="120" customHeight="1">
-      <c r="B21" s="90"/>
-      <c r="C21" s="91"/>
-      <c r="D21" s="91"/>
-      <c r="E21" s="91"/>
-      <c r="F21" s="91"/>
-      <c r="G21" s="91"/>
-      <c r="H21" s="91"/>
-      <c r="I21" s="91"/>
-      <c r="J21" s="91"/>
-      <c r="K21" s="91"/>
-      <c r="L21" s="91"/>
-      <c r="M21" s="91"/>
-      <c r="N21" s="91"/>
-      <c r="O21" s="91"/>
-      <c r="P21" s="91"/>
-      <c r="Q21" s="91"/>
-      <c r="R21" s="91"/>
-      <c r="S21" s="91"/>
-      <c r="T21" s="92"/>
+      <c r="B21" s="86"/>
+      <c r="C21" s="87"/>
+      <c r="D21" s="87"/>
+      <c r="E21" s="87"/>
+      <c r="F21" s="87"/>
+      <c r="G21" s="87"/>
+      <c r="H21" s="87"/>
+      <c r="I21" s="87"/>
+      <c r="J21" s="87"/>
+      <c r="K21" s="87"/>
+      <c r="L21" s="87"/>
+      <c r="M21" s="87"/>
+      <c r="N21" s="87"/>
+      <c r="O21" s="87"/>
+      <c r="P21" s="87"/>
+      <c r="Q21" s="87"/>
+      <c r="R21" s="87"/>
+      <c r="S21" s="87"/>
+      <c r="T21" s="88"/>
     </row>
     <row r="22" spans="2:21" ht="60" customHeight="1">
-      <c r="B22" s="93"/>
-      <c r="C22" s="94"/>
-      <c r="D22" s="94"/>
-      <c r="E22" s="94"/>
-      <c r="F22" s="94"/>
-      <c r="G22" s="94"/>
-      <c r="H22" s="94"/>
-      <c r="I22" s="94"/>
-      <c r="J22" s="94"/>
-      <c r="K22" s="94"/>
-      <c r="L22" s="94"/>
-      <c r="M22" s="94"/>
-      <c r="N22" s="94"/>
-      <c r="O22" s="94"/>
-      <c r="P22" s="94"/>
-      <c r="Q22" s="94"/>
-      <c r="R22" s="94"/>
-      <c r="S22" s="94"/>
-      <c r="T22" s="95"/>
+      <c r="B22" s="89"/>
+      <c r="C22" s="90"/>
+      <c r="D22" s="90"/>
+      <c r="E22" s="90"/>
+      <c r="F22" s="90"/>
+      <c r="G22" s="90"/>
+      <c r="H22" s="90"/>
+      <c r="I22" s="90"/>
+      <c r="J22" s="90"/>
+      <c r="K22" s="90"/>
+      <c r="L22" s="90"/>
+      <c r="M22" s="90"/>
+      <c r="N22" s="90"/>
+      <c r="O22" s="90"/>
+      <c r="P22" s="90"/>
+      <c r="Q22" s="90"/>
+      <c r="R22" s="90"/>
+      <c r="S22" s="90"/>
+      <c r="T22" s="91"/>
     </row>
     <row r="23" spans="2:21" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B23" s="12"/>
@@ -2257,146 +2258,146 @@
       <c r="T23" s="12"/>
     </row>
     <row r="24" spans="2:21" ht="20.100000000000001" customHeight="1">
-      <c r="B24" s="63" t="s">
+      <c r="B24" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="64"/>
-      <c r="D24" s="64"/>
-      <c r="E24" s="64"/>
-      <c r="F24" s="64"/>
-      <c r="G24" s="64"/>
-      <c r="H24" s="64"/>
-      <c r="I24" s="64"/>
-      <c r="J24" s="64"/>
-      <c r="K24" s="64"/>
-      <c r="L24" s="64"/>
-      <c r="M24" s="64"/>
-      <c r="N24" s="64"/>
-      <c r="O24" s="64"/>
-      <c r="P24" s="64"/>
-      <c r="Q24" s="64"/>
-      <c r="R24" s="64"/>
-      <c r="S24" s="64"/>
-      <c r="T24" s="65"/>
+      <c r="C24" s="63"/>
+      <c r="D24" s="63"/>
+      <c r="E24" s="63"/>
+      <c r="F24" s="63"/>
+      <c r="G24" s="63"/>
+      <c r="H24" s="63"/>
+      <c r="I24" s="63"/>
+      <c r="J24" s="63"/>
+      <c r="K24" s="63"/>
+      <c r="L24" s="63"/>
+      <c r="M24" s="63"/>
+      <c r="N24" s="63"/>
+      <c r="O24" s="63"/>
+      <c r="P24" s="63"/>
+      <c r="Q24" s="63"/>
+      <c r="R24" s="63"/>
+      <c r="S24" s="63"/>
+      <c r="T24" s="64"/>
     </row>
     <row r="25" spans="2:21" ht="20.100000000000001" customHeight="1">
-      <c r="B25" s="66" t="s">
+      <c r="B25" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="66" t="s">
+      <c r="C25" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="D25" s="66" t="s">
+      <c r="D25" s="108" t="s">
         <v>27</v>
       </c>
-      <c r="E25" s="66"/>
-      <c r="F25" s="66" t="s">
+      <c r="E25" s="109"/>
+      <c r="F25" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="G25" s="66"/>
-      <c r="H25" s="66" t="s">
+      <c r="G25" s="65"/>
+      <c r="H25" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="I25" s="66"/>
-      <c r="J25" s="66" t="s">
+      <c r="I25" s="65"/>
+      <c r="J25" s="65" t="s">
         <v>30</v>
       </c>
-      <c r="K25" s="66"/>
-      <c r="L25" s="66"/>
-      <c r="M25" s="67" t="s">
+      <c r="K25" s="65"/>
+      <c r="L25" s="65"/>
+      <c r="M25" s="66" t="s">
         <v>31</v>
       </c>
-      <c r="N25" s="66"/>
-      <c r="O25" s="66"/>
-      <c r="P25" s="66" t="s">
+      <c r="N25" s="65"/>
+      <c r="O25" s="65"/>
+      <c r="P25" s="65" t="s">
         <v>32</v>
       </c>
-      <c r="Q25" s="66" t="s">
+      <c r="Q25" s="65" t="s">
         <v>33</v>
       </c>
-      <c r="R25" s="66" t="s">
+      <c r="R25" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="S25" s="66" t="s">
+      <c r="S25" s="65" t="s">
         <v>35</v>
       </c>
-      <c r="T25" s="66" t="s">
+      <c r="T25" s="65" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="26" spans="2:21" ht="19.5" customHeight="1">
-      <c r="B26" s="76"/>
-      <c r="C26" s="77"/>
+      <c r="B26" s="75"/>
+      <c r="C26" s="76"/>
       <c r="D26" s="77"/>
-      <c r="E26" s="77"/>
-      <c r="F26" s="101"/>
-      <c r="G26" s="103"/>
-      <c r="H26" s="78"/>
-      <c r="I26" s="79"/>
+      <c r="E26" s="78"/>
+      <c r="F26" s="97"/>
+      <c r="G26" s="99"/>
+      <c r="H26" s="77"/>
+      <c r="I26" s="78"/>
       <c r="J26" s="77"/>
-      <c r="K26" s="78"/>
-      <c r="L26" s="79"/>
-      <c r="M26" s="101"/>
-      <c r="N26" s="102"/>
-      <c r="O26" s="103"/>
-      <c r="P26" s="77"/>
-      <c r="Q26" s="77"/>
-      <c r="R26" s="77"/>
-      <c r="S26" s="77"/>
-      <c r="T26" s="77"/>
-      <c r="U26" s="60"/>
+      <c r="K26" s="79"/>
+      <c r="L26" s="78"/>
+      <c r="M26" s="97"/>
+      <c r="N26" s="98"/>
+      <c r="O26" s="99"/>
+      <c r="P26" s="76"/>
+      <c r="Q26" s="76"/>
+      <c r="R26" s="76"/>
+      <c r="S26" s="76"/>
+      <c r="T26" s="76"/>
+      <c r="U26" s="59"/>
     </row>
     <row r="27" spans="2:21" ht="19.5" customHeight="1">
-      <c r="B27" s="76"/>
-      <c r="C27" s="77"/>
+      <c r="B27" s="75"/>
+      <c r="C27" s="76"/>
       <c r="D27" s="77"/>
-      <c r="E27" s="77"/>
-      <c r="F27" s="101"/>
-      <c r="G27" s="103"/>
-      <c r="H27" s="78"/>
-      <c r="I27" s="79"/>
+      <c r="E27" s="78"/>
+      <c r="F27" s="97"/>
+      <c r="G27" s="99"/>
+      <c r="H27" s="77"/>
+      <c r="I27" s="78"/>
       <c r="J27" s="77"/>
-      <c r="K27" s="78"/>
-      <c r="L27" s="79"/>
-      <c r="M27" s="78"/>
-      <c r="N27" s="80"/>
-      <c r="O27" s="79"/>
-      <c r="P27" s="77"/>
-      <c r="Q27" s="77"/>
-      <c r="R27" s="77"/>
-      <c r="S27" s="77"/>
-      <c r="T27" s="77"/>
-      <c r="U27" s="60"/>
+      <c r="K27" s="79"/>
+      <c r="L27" s="78"/>
+      <c r="M27" s="77"/>
+      <c r="N27" s="79"/>
+      <c r="O27" s="78"/>
+      <c r="P27" s="76"/>
+      <c r="Q27" s="76"/>
+      <c r="R27" s="76"/>
+      <c r="S27" s="76"/>
+      <c r="T27" s="76"/>
+      <c r="U27" s="59"/>
     </row>
     <row r="28" spans="2:21" ht="19.5" customHeight="1">
-      <c r="B28" s="76"/>
-      <c r="C28" s="77"/>
+      <c r="B28" s="75"/>
+      <c r="C28" s="76"/>
       <c r="D28" s="77"/>
-      <c r="E28" s="77"/>
-      <c r="F28" s="101"/>
-      <c r="G28" s="103"/>
-      <c r="H28" s="78"/>
-      <c r="I28" s="79"/>
+      <c r="E28" s="78"/>
+      <c r="F28" s="97"/>
+      <c r="G28" s="99"/>
+      <c r="H28" s="77"/>
+      <c r="I28" s="78"/>
       <c r="J28" s="77"/>
-      <c r="K28" s="78"/>
-      <c r="L28" s="79"/>
-      <c r="M28" s="78"/>
-      <c r="N28" s="80"/>
-      <c r="O28" s="79"/>
-      <c r="P28" s="77"/>
-      <c r="Q28" s="77"/>
-      <c r="R28" s="77"/>
-      <c r="S28" s="77"/>
-      <c r="T28" s="77"/>
-      <c r="U28" s="60"/>
+      <c r="K28" s="79"/>
+      <c r="L28" s="78"/>
+      <c r="M28" s="77"/>
+      <c r="N28" s="79"/>
+      <c r="O28" s="78"/>
+      <c r="P28" s="76"/>
+      <c r="Q28" s="76"/>
+      <c r="R28" s="76"/>
+      <c r="S28" s="76"/>
+      <c r="T28" s="76"/>
+      <c r="U28" s="59"/>
     </row>
     <row r="29" spans="2:21" ht="19.5" customHeight="1">
-      <c r="B29" s="75"/>
-      <c r="T29" s="81"/>
-      <c r="U29" s="60"/>
+      <c r="B29" s="74"/>
+      <c r="T29" s="80"/>
+      <c r="U29" s="59"/>
     </row>
     <row r="30" spans="2:21" s="32" customFormat="1" ht="60" customHeight="1" thickBot="1">
-      <c r="T30" s="45"/>
+      <c r="T30" s="44"/>
     </row>
     <row r="31" spans="2:21" ht="16.5" thickBot="1">
       <c r="B31" s="14" t="s">
@@ -2439,24 +2440,24 @@
       <c r="H32" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="I32" s="87" t="s">
+      <c r="I32" s="105" t="s">
         <v>42</v>
       </c>
-      <c r="J32" s="88"/>
-      <c r="K32" s="89"/>
-      <c r="L32" s="87" t="s">
+      <c r="J32" s="106"/>
+      <c r="K32" s="107"/>
+      <c r="L32" s="105" t="s">
         <v>43</v>
       </c>
-      <c r="M32" s="88"/>
-      <c r="N32" s="89"/>
-      <c r="O32" s="96" t="s">
+      <c r="M32" s="106"/>
+      <c r="N32" s="107"/>
+      <c r="O32" s="92" t="s">
         <v>44</v>
       </c>
-      <c r="P32" s="97"/>
-      <c r="Q32" s="96" t="s">
+      <c r="P32" s="93"/>
+      <c r="Q32" s="92" t="s">
         <v>45</v>
       </c>
-      <c r="R32" s="97"/>
+      <c r="R32" s="93"/>
       <c r="S32" s="27" t="s">
         <v>46</v>
       </c>
@@ -2467,32 +2468,32 @@
     <row r="33" spans="2:20" ht="30" customHeight="1">
       <c r="B33" s="5"/>
       <c r="C33" s="30"/>
-      <c r="D33" s="98"/>
-      <c r="E33" s="99"/>
-      <c r="F33" s="99"/>
-      <c r="G33" s="100"/>
-      <c r="H33" s="35"/>
-      <c r="I33" s="36"/>
+      <c r="D33" s="94"/>
+      <c r="E33" s="95"/>
+      <c r="F33" s="95"/>
+      <c r="G33" s="96"/>
+      <c r="H33" s="34"/>
+      <c r="I33" s="35"/>
       <c r="J33" s="6"/>
       <c r="K33" s="30"/>
-      <c r="L33" s="36"/>
+      <c r="L33" s="35"/>
       <c r="M33" s="6"/>
       <c r="N33" s="30"/>
-      <c r="O33" s="36"/>
+      <c r="O33" s="35"/>
       <c r="P33" s="30"/>
-      <c r="Q33" s="36"/>
+      <c r="Q33" s="35"/>
       <c r="R33" s="30"/>
-      <c r="S33" s="38"/>
-      <c r="T33" s="37"/>
+      <c r="S33" s="37"/>
+      <c r="T33" s="36"/>
     </row>
     <row r="34" spans="2:20" ht="30" customHeight="1">
       <c r="B34" s="8"/>
       <c r="C34" s="22"/>
-      <c r="D34" s="83"/>
-      <c r="E34" s="84"/>
-      <c r="F34" s="84"/>
-      <c r="G34" s="85"/>
-      <c r="H34" s="47"/>
+      <c r="D34" s="101"/>
+      <c r="E34" s="102"/>
+      <c r="F34" s="102"/>
+      <c r="G34" s="103"/>
+      <c r="H34" s="46"/>
       <c r="I34" s="10"/>
       <c r="J34" s="9"/>
       <c r="K34" s="22"/>
@@ -2503,7 +2504,7 @@
       <c r="P34" s="22"/>
       <c r="Q34" s="10"/>
       <c r="R34" s="22"/>
-      <c r="S34" s="45"/>
+      <c r="S34" s="44"/>
       <c r="T34" s="23"/>
     </row>
     <row r="35" spans="2:20" ht="30" customHeight="1">
@@ -2513,7 +2514,7 @@
       <c r="E35" s="9"/>
       <c r="F35" s="9"/>
       <c r="G35" s="22"/>
-      <c r="H35" s="47"/>
+      <c r="H35" s="46"/>
       <c r="I35" s="10"/>
       <c r="J35" s="9"/>
       <c r="K35" s="22"/>
@@ -2524,7 +2525,7 @@
       <c r="P35" s="22"/>
       <c r="Q35" s="10"/>
       <c r="R35" s="22"/>
-      <c r="S35" s="45"/>
+      <c r="S35" s="44"/>
       <c r="T35" s="23"/>
     </row>
     <row r="36" spans="2:20" ht="30" customHeight="1">
@@ -2534,7 +2535,7 @@
       <c r="E36" s="9"/>
       <c r="F36" s="9"/>
       <c r="G36" s="22"/>
-      <c r="H36" s="47"/>
+      <c r="H36" s="46"/>
       <c r="I36" s="10"/>
       <c r="J36" s="9"/>
       <c r="K36" s="22"/>
@@ -2545,17 +2546,17 @@
       <c r="P36" s="22"/>
       <c r="Q36" s="10"/>
       <c r="R36" s="22"/>
-      <c r="S36" s="45"/>
+      <c r="S36" s="44"/>
       <c r="T36" s="23"/>
     </row>
     <row r="37" spans="2:20" ht="30" customHeight="1">
       <c r="B37" s="8"/>
       <c r="C37" s="22"/>
-      <c r="D37" s="48"/>
-      <c r="E37" s="49"/>
-      <c r="F37" s="49"/>
-      <c r="G37" s="50"/>
-      <c r="H37" s="47"/>
+      <c r="D37" s="47"/>
+      <c r="E37" s="48"/>
+      <c r="F37" s="48"/>
+      <c r="G37" s="49"/>
+      <c r="H37" s="46"/>
       <c r="I37" s="10"/>
       <c r="J37" s="9"/>
       <c r="K37" s="22"/>
@@ -2566,17 +2567,17 @@
       <c r="P37" s="22"/>
       <c r="Q37" s="10"/>
       <c r="R37" s="22"/>
-      <c r="S37" s="45"/>
+      <c r="S37" s="44"/>
       <c r="T37" s="23"/>
     </row>
     <row r="38" spans="2:20" ht="30" customHeight="1">
       <c r="B38" s="8"/>
       <c r="C38" s="22"/>
       <c r="D38" s="10"/>
-      <c r="E38" s="54"/>
-      <c r="F38" s="54"/>
-      <c r="G38" s="55"/>
-      <c r="H38" s="47"/>
+      <c r="E38" s="53"/>
+      <c r="F38" s="53"/>
+      <c r="G38" s="54"/>
+      <c r="H38" s="46"/>
       <c r="I38" s="10"/>
       <c r="J38" s="9"/>
       <c r="K38" s="22"/>
@@ -2587,38 +2588,38 @@
       <c r="P38" s="22"/>
       <c r="Q38" s="10"/>
       <c r="R38" s="22"/>
-      <c r="S38" s="45"/>
+      <c r="S38" s="44"/>
       <c r="T38" s="23"/>
     </row>
-    <row r="39" spans="2:20" s="39" customFormat="1" ht="30" customHeight="1">
-      <c r="B39" s="40"/>
-      <c r="C39" s="43"/>
-      <c r="D39" s="42"/>
-      <c r="E39" s="41"/>
-      <c r="F39" s="41"/>
-      <c r="G39" s="43"/>
-      <c r="H39" s="51"/>
-      <c r="I39" s="42"/>
-      <c r="J39" s="41"/>
-      <c r="K39" s="43"/>
-      <c r="L39" s="42"/>
-      <c r="M39" s="41"/>
-      <c r="N39" s="43"/>
-      <c r="O39" s="42"/>
-      <c r="P39" s="43"/>
-      <c r="Q39" s="42"/>
-      <c r="R39" s="43"/>
-      <c r="S39" s="46"/>
-      <c r="T39" s="44"/>
+    <row r="39" spans="2:20" s="38" customFormat="1" ht="30" customHeight="1">
+      <c r="B39" s="39"/>
+      <c r="C39" s="42"/>
+      <c r="D39" s="41"/>
+      <c r="E39" s="40"/>
+      <c r="F39" s="40"/>
+      <c r="G39" s="42"/>
+      <c r="H39" s="50"/>
+      <c r="I39" s="41"/>
+      <c r="J39" s="40"/>
+      <c r="K39" s="42"/>
+      <c r="L39" s="41"/>
+      <c r="M39" s="40"/>
+      <c r="N39" s="42"/>
+      <c r="O39" s="41"/>
+      <c r="P39" s="42"/>
+      <c r="Q39" s="41"/>
+      <c r="R39" s="42"/>
+      <c r="S39" s="45"/>
+      <c r="T39" s="43"/>
     </row>
     <row r="40" spans="2:20" ht="30" customHeight="1">
       <c r="B40" s="8"/>
       <c r="C40" s="22"/>
       <c r="D40" s="10"/>
-      <c r="E40" s="52"/>
-      <c r="F40" s="52"/>
-      <c r="G40" s="53"/>
-      <c r="H40" s="47"/>
+      <c r="E40" s="51"/>
+      <c r="F40" s="51"/>
+      <c r="G40" s="52"/>
+      <c r="H40" s="46"/>
       <c r="I40" s="10"/>
       <c r="J40" s="9"/>
       <c r="K40" s="22"/>
@@ -2629,17 +2630,17 @@
       <c r="P40" s="22"/>
       <c r="Q40" s="10"/>
       <c r="R40" s="22"/>
-      <c r="S40" s="45"/>
+      <c r="S40" s="44"/>
       <c r="T40" s="23"/>
     </row>
     <row r="41" spans="2:20" ht="30" customHeight="1">
       <c r="B41" s="8"/>
       <c r="C41" s="22"/>
       <c r="D41" s="10"/>
-      <c r="E41" s="52"/>
-      <c r="F41" s="52"/>
-      <c r="G41" s="53"/>
-      <c r="H41" s="47"/>
+      <c r="E41" s="51"/>
+      <c r="F41" s="51"/>
+      <c r="G41" s="52"/>
+      <c r="H41" s="46"/>
       <c r="I41" s="10"/>
       <c r="J41" s="9"/>
       <c r="K41" s="22"/>
@@ -2650,7 +2651,7 @@
       <c r="P41" s="22"/>
       <c r="Q41" s="10"/>
       <c r="R41" s="22"/>
-      <c r="S41" s="45"/>
+      <c r="S41" s="44"/>
       <c r="T41" s="23"/>
     </row>
     <row r="42" spans="2:20" ht="30" customHeight="1">
@@ -2660,7 +2661,7 @@
       <c r="E42" s="9"/>
       <c r="F42" s="9"/>
       <c r="G42" s="22"/>
-      <c r="H42" s="47"/>
+      <c r="H42" s="46"/>
       <c r="I42" s="10"/>
       <c r="J42" s="9"/>
       <c r="K42" s="22"/>
@@ -2671,7 +2672,7 @@
       <c r="P42" s="22"/>
       <c r="Q42" s="10"/>
       <c r="R42" s="22"/>
-      <c r="S42" s="45"/>
+      <c r="S42" s="44"/>
       <c r="T42" s="23"/>
     </row>
     <row r="43" spans="2:20" ht="30" customHeight="1">
@@ -2681,7 +2682,7 @@
       <c r="E43" s="9"/>
       <c r="F43" s="9"/>
       <c r="G43" s="22"/>
-      <c r="H43" s="47"/>
+      <c r="H43" s="46"/>
       <c r="I43" s="10"/>
       <c r="J43" s="9"/>
       <c r="K43" s="22"/>
@@ -2692,17 +2693,17 @@
       <c r="P43" s="22"/>
       <c r="Q43" s="10"/>
       <c r="R43" s="22"/>
-      <c r="S43" s="45"/>
+      <c r="S43" s="44"/>
       <c r="T43" s="23"/>
     </row>
     <row r="44" spans="2:20" ht="30" customHeight="1">
-      <c r="B44" s="42"/>
-      <c r="C44" s="43"/>
-      <c r="D44" s="42"/>
-      <c r="E44" s="41"/>
-      <c r="F44" s="41"/>
-      <c r="G44" s="43"/>
-      <c r="H44" s="47"/>
+      <c r="B44" s="41"/>
+      <c r="C44" s="42"/>
+      <c r="D44" s="41"/>
+      <c r="E44" s="40"/>
+      <c r="F44" s="40"/>
+      <c r="G44" s="42"/>
+      <c r="H44" s="46"/>
       <c r="I44" s="10"/>
       <c r="J44" s="9"/>
       <c r="K44" s="22"/>
@@ -2713,17 +2714,17 @@
       <c r="P44" s="22"/>
       <c r="Q44" s="10"/>
       <c r="R44" s="22"/>
-      <c r="S44" s="45"/>
+      <c r="S44" s="44"/>
       <c r="T44" s="23"/>
     </row>
     <row r="45" spans="2:20" ht="30" customHeight="1">
       <c r="B45" s="8"/>
       <c r="C45" s="22"/>
       <c r="D45" s="10"/>
-      <c r="E45" s="54"/>
-      <c r="F45" s="54"/>
-      <c r="G45" s="55"/>
-      <c r="H45" s="47"/>
+      <c r="E45" s="53"/>
+      <c r="F45" s="53"/>
+      <c r="G45" s="54"/>
+      <c r="H45" s="46"/>
       <c r="I45" s="10"/>
       <c r="J45" s="9"/>
       <c r="K45" s="22"/>
@@ -2734,17 +2735,17 @@
       <c r="P45" s="22"/>
       <c r="Q45" s="10"/>
       <c r="R45" s="22"/>
-      <c r="S45" s="45"/>
+      <c r="S45" s="44"/>
       <c r="T45" s="23"/>
     </row>
     <row r="46" spans="2:20" ht="30" customHeight="1">
       <c r="B46" s="8"/>
       <c r="C46" s="22"/>
       <c r="D46" s="10"/>
-      <c r="E46" s="52"/>
-      <c r="F46" s="52"/>
-      <c r="G46" s="53"/>
-      <c r="H46" s="47"/>
+      <c r="E46" s="51"/>
+      <c r="F46" s="51"/>
+      <c r="G46" s="52"/>
+      <c r="H46" s="46"/>
       <c r="I46" s="10"/>
       <c r="J46" s="9"/>
       <c r="K46" s="22"/>
@@ -2755,17 +2756,17 @@
       <c r="P46" s="22"/>
       <c r="Q46" s="10"/>
       <c r="R46" s="22"/>
-      <c r="S46" s="45"/>
+      <c r="S46" s="44"/>
       <c r="T46" s="23"/>
     </row>
     <row r="47" spans="2:20" ht="30" customHeight="1" thickBot="1">
       <c r="B47" s="8"/>
       <c r="C47" s="22"/>
       <c r="D47" s="10"/>
-      <c r="E47" s="52"/>
-      <c r="F47" s="52"/>
-      <c r="G47" s="53"/>
-      <c r="H47" s="47"/>
+      <c r="E47" s="51"/>
+      <c r="F47" s="51"/>
+      <c r="G47" s="52"/>
+      <c r="H47" s="46"/>
       <c r="I47" s="10"/>
       <c r="J47" s="9"/>
       <c r="K47" s="22"/>
@@ -2776,7 +2777,7 @@
       <c r="P47" s="22"/>
       <c r="Q47" s="10"/>
       <c r="R47" s="22"/>
-      <c r="S47" s="45"/>
+      <c r="S47" s="44"/>
       <c r="T47" s="23"/>
     </row>
     <row r="48" spans="2:20" ht="9.9499999999999993" customHeight="1">
@@ -2821,67 +2822,136 @@
         <v>50</v>
       </c>
     </row>
-    <row r="51" spans="2:20" ht="14.25" customHeight="1">
-      <c r="K51" s="86"/>
-      <c r="L51" s="86"/>
+    <row r="51" spans="2:20" ht="14.25" customHeight="1" thickBot="1">
+      <c r="K51" s="104"/>
+      <c r="L51" s="104"/>
       <c r="T51" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="52" spans="2:20" ht="16.5" customHeight="1" thickBot="1">
-      <c r="B52" s="33"/>
-      <c r="C52" s="33"/>
-      <c r="D52" s="33"/>
-      <c r="E52" s="33"/>
-      <c r="F52" s="33"/>
-      <c r="G52" s="33"/>
-      <c r="H52" s="33"/>
-      <c r="I52" s="33"/>
-      <c r="J52" s="33"/>
-      <c r="K52" s="33"/>
-      <c r="L52" s="33"/>
-      <c r="M52" s="33"/>
-      <c r="N52" s="33"/>
-      <c r="O52" s="33"/>
-      <c r="P52" s="33"/>
-      <c r="Q52" s="33"/>
-      <c r="R52" s="33"/>
-      <c r="S52" s="33"/>
-      <c r="T52" s="33"/>
-    </row>
-    <row r="53" spans="2:20" ht="16.5" customHeight="1"/>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="52" spans="2:20" ht="16.5" customHeight="1">
+      <c r="B52" s="83"/>
+      <c r="C52" s="83"/>
+      <c r="D52" s="83"/>
+      <c r="E52" s="83"/>
+      <c r="F52" s="83"/>
+      <c r="G52" s="83"/>
+      <c r="H52" s="83"/>
+      <c r="I52" s="83"/>
+      <c r="J52" s="83"/>
+      <c r="K52" s="83"/>
+      <c r="L52" s="83"/>
+      <c r="M52" s="83"/>
+      <c r="N52" s="83"/>
+      <c r="O52" s="83"/>
+      <c r="P52" s="83"/>
+      <c r="Q52" s="83"/>
+      <c r="R52" s="83"/>
+      <c r="S52" s="83"/>
+      <c r="T52" s="83"/>
+    </row>
+    <row r="53" spans="2:20" ht="16.5" customHeight="1">
+      <c r="B53" s="84" t="s">
+        <v>48</v>
+      </c>
+      <c r="C53" s="84"/>
+      <c r="D53" s="84"/>
+      <c r="E53" s="84"/>
+      <c r="F53" s="84"/>
+      <c r="G53" s="84"/>
+      <c r="H53" s="84"/>
+      <c r="I53" s="84"/>
+      <c r="J53" s="84" t="s">
+        <v>49</v>
+      </c>
+      <c r="K53" s="84"/>
+      <c r="L53" s="84"/>
+      <c r="M53" s="84"/>
+      <c r="N53" s="84"/>
+      <c r="O53" s="84"/>
+      <c r="P53" s="84"/>
+      <c r="Q53" s="84"/>
+      <c r="R53" s="84" t="s">
+        <v>53</v>
+      </c>
+      <c r="S53" s="84"/>
+      <c r="T53" s="84"/>
+    </row>
     <row r="54" spans="2:20" ht="16.5" customHeight="1">
-      <c r="B54" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="B54" s="84"/>
+      <c r="C54" s="84"/>
+      <c r="D54" s="84"/>
+      <c r="E54" s="84"/>
+      <c r="F54" s="84"/>
+      <c r="G54" s="84"/>
+      <c r="H54" s="84"/>
+      <c r="I54" s="84"/>
+      <c r="J54" s="84"/>
+      <c r="K54" s="84" t="s">
+        <v>50</v>
+      </c>
+      <c r="L54" s="84"/>
+      <c r="M54" s="84"/>
+      <c r="N54" s="84"/>
+      <c r="O54" s="84"/>
+      <c r="P54" s="84"/>
+      <c r="Q54" s="84"/>
+      <c r="R54" s="84"/>
+      <c r="S54" s="84"/>
+      <c r="T54" s="84"/>
     </row>
     <row r="55" spans="2:20" s="31" customFormat="1">
-      <c r="B55" s="31" t="s">
+      <c r="B55" s="84" t="s">
+        <v>54</v>
+      </c>
+      <c r="C55" s="84"/>
+      <c r="D55" s="84"/>
+      <c r="E55" s="84"/>
+      <c r="F55" s="84"/>
+      <c r="G55" s="84"/>
+      <c r="H55" s="84"/>
+      <c r="I55" s="84"/>
+      <c r="J55" s="84"/>
+      <c r="K55" s="100"/>
+      <c r="L55" s="100"/>
+      <c r="M55" s="84"/>
+      <c r="N55" s="84"/>
+      <c r="O55" s="84"/>
+      <c r="P55" s="84"/>
+      <c r="Q55" s="84"/>
+      <c r="R55" s="84"/>
+      <c r="S55" s="84"/>
+      <c r="T55" s="84" t="s">
         <v>52</v>
       </c>
-      <c r="C55" s="31" t="s">
-        <v>53</v>
-      </c>
-      <c r="D55" s="31" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="56" spans="2:20" s="31" customFormat="1">
-      <c r="B56" s="31">
-        <v>0</v>
-      </c>
-      <c r="C56" s="34">
-        <v>46119</v>
-      </c>
-      <c r="D56" s="31" t="s">
-        <v>55</v>
-      </c>
+    </row>
+    <row r="56" spans="2:20" s="31" customFormat="1" ht="15" thickBot="1">
+      <c r="B56" s="85"/>
+      <c r="C56" s="85"/>
+      <c r="D56" s="85"/>
+      <c r="E56" s="85"/>
+      <c r="F56" s="85"/>
+      <c r="G56" s="85"/>
+      <c r="H56" s="85"/>
+      <c r="I56" s="85"/>
+      <c r="J56" s="85"/>
+      <c r="K56" s="85"/>
+      <c r="L56" s="85"/>
+      <c r="M56" s="85"/>
+      <c r="N56" s="85"/>
+      <c r="O56" s="85"/>
+      <c r="P56" s="85"/>
+      <c r="Q56" s="85"/>
+      <c r="R56" s="85"/>
+      <c r="S56" s="85"/>
+      <c r="T56" s="85"/>
     </row>
     <row r="57" spans="2:20" s="31" customFormat="1">
-      <c r="C57" s="34"/>
+      <c r="C57" s="33"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
+    <mergeCell ref="K55:L55"/>
     <mergeCell ref="D34:G34"/>
     <mergeCell ref="K51:L51"/>
     <mergeCell ref="I32:K32"/>

--- a/Rel Website/backend/templates/REL LTC Template.xlsx
+++ b/Rel Website/backend/templates/REL LTC Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amkor-my.sharepoint.com/personal/francisnino_villanueva_amkor_com/Documents/Documents/GitHub/Rel Request Process Flow/Rel Website/backend/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="8_{55472A56-189D-460A-834D-19C0FE061C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B78F68D-4A9A-4534-B89D-92D23FB2DDF7}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="8_{55472A56-189D-460A-834D-19C0FE061C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24C4256D-2630-42FA-B465-31E3D30E8790}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1350" yWindow="1950" windowWidth="27450" windowHeight="9990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1131,6 +1131,36 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1172,36 +1202,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="9">
@@ -1304,202 +1304,11 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>117242</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>30873</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>318881</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>214724</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="Rectangle 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A76155A2-70B2-4CA8-8A20-DF3B6EE63D92}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2416849" y="26728087"/>
-          <a:ext cx="201639" cy="183851"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="19050">
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:endParaRPr lang="en-PH"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>133145</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>30874</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>334235</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>202924</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="Rectangle 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CDFE29FD-AE8D-4F68-8194-EC60CB3A8E79}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2868181" y="26728088"/>
-          <a:ext cx="201090" cy="172050"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="19050">
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:endParaRPr lang="en-PH"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>142874</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>35719</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>343964</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>207769</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="Rectangle 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3762D108-DDAC-4A68-BD66-2362739EBE63}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3313338" y="26732933"/>
-          <a:ext cx="201090" cy="172050"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="19050">
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:endParaRPr lang="en-PH"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2195,46 +2004,46 @@
       <c r="T20" s="16"/>
     </row>
     <row r="21" spans="2:21" ht="120" customHeight="1">
-      <c r="B21" s="86"/>
-      <c r="C21" s="87"/>
-      <c r="D21" s="87"/>
-      <c r="E21" s="87"/>
-      <c r="F21" s="87"/>
-      <c r="G21" s="87"/>
-      <c r="H21" s="87"/>
-      <c r="I21" s="87"/>
-      <c r="J21" s="87"/>
-      <c r="K21" s="87"/>
-      <c r="L21" s="87"/>
-      <c r="M21" s="87"/>
-      <c r="N21" s="87"/>
-      <c r="O21" s="87"/>
-      <c r="P21" s="87"/>
-      <c r="Q21" s="87"/>
-      <c r="R21" s="87"/>
-      <c r="S21" s="87"/>
-      <c r="T21" s="88"/>
+      <c r="B21" s="96"/>
+      <c r="C21" s="97"/>
+      <c r="D21" s="97"/>
+      <c r="E21" s="97"/>
+      <c r="F21" s="97"/>
+      <c r="G21" s="97"/>
+      <c r="H21" s="97"/>
+      <c r="I21" s="97"/>
+      <c r="J21" s="97"/>
+      <c r="K21" s="97"/>
+      <c r="L21" s="97"/>
+      <c r="M21" s="97"/>
+      <c r="N21" s="97"/>
+      <c r="O21" s="97"/>
+      <c r="P21" s="97"/>
+      <c r="Q21" s="97"/>
+      <c r="R21" s="97"/>
+      <c r="S21" s="97"/>
+      <c r="T21" s="98"/>
     </row>
     <row r="22" spans="2:21" ht="60" customHeight="1">
-      <c r="B22" s="89"/>
-      <c r="C22" s="90"/>
-      <c r="D22" s="90"/>
-      <c r="E22" s="90"/>
-      <c r="F22" s="90"/>
-      <c r="G22" s="90"/>
-      <c r="H22" s="90"/>
-      <c r="I22" s="90"/>
-      <c r="J22" s="90"/>
-      <c r="K22" s="90"/>
-      <c r="L22" s="90"/>
-      <c r="M22" s="90"/>
-      <c r="N22" s="90"/>
-      <c r="O22" s="90"/>
-      <c r="P22" s="90"/>
-      <c r="Q22" s="90"/>
-      <c r="R22" s="90"/>
-      <c r="S22" s="90"/>
-      <c r="T22" s="91"/>
+      <c r="B22" s="99"/>
+      <c r="C22" s="100"/>
+      <c r="D22" s="100"/>
+      <c r="E22" s="100"/>
+      <c r="F22" s="100"/>
+      <c r="G22" s="100"/>
+      <c r="H22" s="100"/>
+      <c r="I22" s="100"/>
+      <c r="J22" s="100"/>
+      <c r="K22" s="100"/>
+      <c r="L22" s="100"/>
+      <c r="M22" s="100"/>
+      <c r="N22" s="100"/>
+      <c r="O22" s="100"/>
+      <c r="P22" s="100"/>
+      <c r="Q22" s="100"/>
+      <c r="R22" s="100"/>
+      <c r="S22" s="100"/>
+      <c r="T22" s="101"/>
     </row>
     <row r="23" spans="2:21" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B23" s="12"/>
@@ -2287,10 +2096,10 @@
       <c r="C25" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="D25" s="108" t="s">
+      <c r="D25" s="86" t="s">
         <v>27</v>
       </c>
-      <c r="E25" s="109"/>
+      <c r="E25" s="87"/>
       <c r="F25" s="65" t="s">
         <v>28</v>
       </c>
@@ -2330,16 +2139,16 @@
       <c r="C26" s="76"/>
       <c r="D26" s="77"/>
       <c r="E26" s="78"/>
-      <c r="F26" s="97"/>
-      <c r="G26" s="99"/>
+      <c r="F26" s="107"/>
+      <c r="G26" s="109"/>
       <c r="H26" s="77"/>
       <c r="I26" s="78"/>
       <c r="J26" s="77"/>
       <c r="K26" s="79"/>
       <c r="L26" s="78"/>
-      <c r="M26" s="97"/>
-      <c r="N26" s="98"/>
-      <c r="O26" s="99"/>
+      <c r="M26" s="107"/>
+      <c r="N26" s="108"/>
+      <c r="O26" s="109"/>
       <c r="P26" s="76"/>
       <c r="Q26" s="76"/>
       <c r="R26" s="76"/>
@@ -2352,8 +2161,8 @@
       <c r="C27" s="76"/>
       <c r="D27" s="77"/>
       <c r="E27" s="78"/>
-      <c r="F27" s="97"/>
-      <c r="G27" s="99"/>
+      <c r="F27" s="107"/>
+      <c r="G27" s="109"/>
       <c r="H27" s="77"/>
       <c r="I27" s="78"/>
       <c r="J27" s="77"/>
@@ -2374,8 +2183,8 @@
       <c r="C28" s="76"/>
       <c r="D28" s="77"/>
       <c r="E28" s="78"/>
-      <c r="F28" s="97"/>
-      <c r="G28" s="99"/>
+      <c r="F28" s="107"/>
+      <c r="G28" s="109"/>
       <c r="H28" s="77"/>
       <c r="I28" s="78"/>
       <c r="J28" s="77"/>
@@ -2440,24 +2249,24 @@
       <c r="H32" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="I32" s="105" t="s">
+      <c r="I32" s="93" t="s">
         <v>42</v>
       </c>
-      <c r="J32" s="106"/>
-      <c r="K32" s="107"/>
-      <c r="L32" s="105" t="s">
+      <c r="J32" s="94"/>
+      <c r="K32" s="95"/>
+      <c r="L32" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="M32" s="106"/>
-      <c r="N32" s="107"/>
-      <c r="O32" s="92" t="s">
+      <c r="M32" s="94"/>
+      <c r="N32" s="95"/>
+      <c r="O32" s="102" t="s">
         <v>44</v>
       </c>
-      <c r="P32" s="93"/>
-      <c r="Q32" s="92" t="s">
+      <c r="P32" s="103"/>
+      <c r="Q32" s="102" t="s">
         <v>45</v>
       </c>
-      <c r="R32" s="93"/>
+      <c r="R32" s="103"/>
       <c r="S32" s="27" t="s">
         <v>46</v>
       </c>
@@ -2468,10 +2277,10 @@
     <row r="33" spans="2:20" ht="30" customHeight="1">
       <c r="B33" s="5"/>
       <c r="C33" s="30"/>
-      <c r="D33" s="94"/>
-      <c r="E33" s="95"/>
-      <c r="F33" s="95"/>
-      <c r="G33" s="96"/>
+      <c r="D33" s="104"/>
+      <c r="E33" s="105"/>
+      <c r="F33" s="105"/>
+      <c r="G33" s="106"/>
       <c r="H33" s="34"/>
       <c r="I33" s="35"/>
       <c r="J33" s="6"/>
@@ -2489,10 +2298,10 @@
     <row r="34" spans="2:20" ht="30" customHeight="1">
       <c r="B34" s="8"/>
       <c r="C34" s="22"/>
-      <c r="D34" s="101"/>
-      <c r="E34" s="102"/>
-      <c r="F34" s="102"/>
-      <c r="G34" s="103"/>
+      <c r="D34" s="89"/>
+      <c r="E34" s="90"/>
+      <c r="F34" s="90"/>
+      <c r="G34" s="91"/>
       <c r="H34" s="46"/>
       <c r="I34" s="10"/>
       <c r="J34" s="9"/>
@@ -2823,8 +2632,8 @@
       </c>
     </row>
     <row r="51" spans="2:20" ht="14.25" customHeight="1" thickBot="1">
-      <c r="K51" s="104"/>
-      <c r="L51" s="104"/>
+      <c r="K51" s="92"/>
+      <c r="L51" s="92"/>
       <c r="T51" s="1" t="s">
         <v>52</v>
       </c>
@@ -2912,8 +2721,8 @@
       <c r="H55" s="84"/>
       <c r="I55" s="84"/>
       <c r="J55" s="84"/>
-      <c r="K55" s="100"/>
-      <c r="L55" s="100"/>
+      <c r="K55" s="88"/>
+      <c r="L55" s="88"/>
       <c r="M55" s="84"/>
       <c r="N55" s="84"/>
       <c r="O55" s="84"/>
@@ -2951,11 +2760,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="K55:L55"/>
-    <mergeCell ref="D34:G34"/>
-    <mergeCell ref="K51:L51"/>
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="L32:N32"/>
     <mergeCell ref="B21:T21"/>
     <mergeCell ref="B22:T22"/>
     <mergeCell ref="O32:P32"/>
@@ -2965,6 +2769,11 @@
     <mergeCell ref="F26:G26"/>
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="F28:G28"/>
+    <mergeCell ref="K55:L55"/>
+    <mergeCell ref="D34:G34"/>
+    <mergeCell ref="K51:L51"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="L32:N32"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
